--- a/outputs/165-23.xlsx
+++ b/outputs/165-23.xlsx
@@ -712,59 +712,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
